--- a/forms/trg/Formulir_TRG_pbudget.xlsx
+++ b/forms/trg/Formulir_TRG_pbudget.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,22 +925,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Darmawati, MSi.,Ak.,CA</t>
+          <t>Dr. Ratna Ayu Damayanti, Ak.,MSoc.Sc.,CA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Economics and Business, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Public Sector Accounting, Local Government Finance, Environmental Accounting</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -949,17 +945,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0536-3225</t>
+          <t>0000-0002-2867-6315</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6038742</t>
+          <t>6026234</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57204544475</t>
+          <t>57191409590</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -974,12 +970,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Syarifuddin, Ak.,MSoc.Sc.,CA</t>
+          <t>Prof. Dr. Darmawati, MSi.,Ak.,CA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Political Budgeting, Public Sector Accounting, Auditing</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -998,17 +994,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7880-9331</t>
+          <t>0000-0003-0536-3225</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6026231</t>
+          <t>6038742</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57219211497</t>
+          <t>57204544475</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1023,22 +1019,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Dileep Kumar M</t>
+          <t>Prof. Dr. Syarifuddin, Ak.,MSoc.Sc.,CA</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Hensard University, Nigeria</t>
+          <t>Faculty of Economics and Business, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Behavioural Sciences, Entrepreneurship &amp; Technology</t>
+          <t>Political Budgeting, Public Sector Accounting, Auditing</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1047,11 +1043,19 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7777-3907</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+          <t>0000-0002-7880-9331</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6026231</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57219211497</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1064,21 +1068,33 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Teri</t>
+          <t>Prof. Dr. Dileep Kumar M</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Hensard University, Nigeria</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Behavioural Sciences, Entrepreneurship &amp; Technology</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-7777-3907</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1109,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Vica Vanessa</t>
+          <t>Teri</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1122,12 +1138,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Gafur Kadar</t>
+          <t>Vica Vanessa</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1149,10 +1165,22 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Muhammad Gafur Kadar</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the Public Budgeting Research Group Explore our resources, engage with our research, and join us in making a meaningful impact on public finance systems world-wide. Thank you for visiting, and we look forward to collaborating with you.</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1160,7 +1188,11 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1349,15 +1381,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
